--- a/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 4,13</t>
+          <t>0,68; 3,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,46</t>
+          <t>1,37; 4,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,2</t>
+          <t>1,34; 3,37</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,96; 17,31</t>
+          <t>9,11; 17,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,13; 11,91</t>
+          <t>7,27; 11,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 13,71</t>
+          <t>8,84; 13,73</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,52</t>
+          <t>5,6; 11,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,54</t>
+          <t>5,03; 9,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,83; 9,73</t>
+          <t>5,69; 9,53</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,54; 14,01</t>
+          <t>5,53; 13,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,46</t>
+          <t>3,06; 8,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,49; 9,32</t>
+          <t>4,58; 9,34</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,86</t>
+          <t>0,37; 2,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,36</t>
+          <t>1,71; 6,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,42</t>
+          <t>1,51; 4,39</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,78</t>
+          <t>8,51; 15,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,35</t>
+          <t>5,84; 10,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,09</t>
+          <t>7,76; 11,79</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 6,8</t>
+          <t>3,22; 6,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,97; 64,99</t>
+          <t>9,9; 66,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 52,17</t>
+          <t>7,21; 50,13</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,65; 18,48</t>
+          <t>4,88; 18,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,82; 21,36</t>
+          <t>16,02; 21,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,5; 18,83</t>
+          <t>9,89; 18,76</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,92; 10,14</t>
+          <t>6,84; 10,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,31; 32,74</t>
+          <t>9,24; 30,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,86; 21,95</t>
+          <t>8,88; 20,44</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre)</t>
+          <t>Hogares con problemas estructurales en la vivienda (goteras, humedades, podredumbre) (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2262; 12847</t>
+          <t>2112; 11130</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4027; 12921</t>
+          <t>3965; 12251</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7120; 19221</t>
+          <t>8026; 20258</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>46472; 89742</t>
+          <t>47204; 92817</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>36641; 61161</t>
+          <t>37318; 61415</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92406; 141500</t>
+          <t>91241; 141696</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17931; 39431</t>
+          <t>17647; 36703</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>16935; 33293</t>
+          <t>17545; 33322</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38748; 64631</t>
+          <t>37762; 63305</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17327; 43779</t>
+          <t>17293; 43341</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14061; 40190</t>
+          <t>14544; 41517</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35359; 73432</t>
+          <t>36060; 73572</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>625; 5116</t>
+          <t>654; 5332</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4030; 16456</t>
+          <t>4436; 17074</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6326; 19330</t>
+          <t>6605; 19208</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>21968; 39846</t>
+          <t>22939; 41760</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15239; 29174</t>
+          <t>15010; 27889</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39914; 63699</t>
+          <t>40877; 62102</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20587; 42427</t>
+          <t>20087; 42032</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>84582; 551494</t>
+          <t>83990; 566191</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>107902; 768341</t>
+          <t>106171; 738241</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>52429; 171588</t>
+          <t>45276; 172027</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>113575; 153325</t>
+          <t>114973; 153232</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>156468; 310038</t>
+          <t>162756; 308949</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>239361; 350675</t>
+          <t>236586; 347832</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>345188; 1214652</t>
+          <t>342711; 1145201</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>634823; 1573330</t>
+          <t>636630; 1465444</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/ProbViv_estruc-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,57</t>
+          <t>1,8; 5,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,23</t>
+          <t>1,41; 4,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,37</t>
+          <t>1,9; 4,28</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 17,9</t>
+          <t>8,75; 16,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,27; 11,96</t>
+          <t>7,26; 11,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 13,73</t>
+          <t>8,38; 12,88</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 11,65</t>
+          <t>6,27; 13,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,54</t>
+          <t>5,64; 10,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,53</t>
+          <t>6,52; 10,54</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 13,87</t>
+          <t>5,6; 13,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,06; 8,74</t>
+          <t>5,67; 11,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 9,34</t>
+          <t>6,24; 11,16</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,98</t>
+          <t>0,97; 5,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,6</t>
+          <t>2,75; 7,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 4,39</t>
+          <t>2,34; 5,59</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,49</t>
+          <t>8,97; 16,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5,84; 10,85</t>
+          <t>6,27; 11,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,79</t>
+          <t>8,3; 12,99</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,73</t>
+          <t>3,98; 7,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,9; 66,73</t>
+          <t>9,0; 13,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7,21; 50,13</t>
+          <t>7,01; 9,8</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 18,52</t>
+          <t>15,1; 20,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,02; 21,35</t>
+          <t>15,45; 20,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,89; 18,76</t>
+          <t>16,04; 19,48</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,84; 10,06</t>
+          <t>9,02; 11,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9,24; 30,87</t>
+          <t>9,47; 11,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,88; 20,44</t>
+          <t>9,47; 10,99</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>10741</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>18477</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2112; 11130</t>
+          <t>5739; 18376</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3965; 12251</t>
+          <t>4459; 12831</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8026; 20258</t>
+          <t>12034; 27188</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>65224</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>48236</t>
+          <t>50583</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113460</t>
+          <t>113470</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>47204; 92817</t>
+          <t>46431; 85333</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37318; 61415</t>
+          <t>39568; 64173</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91241; 141696</t>
+          <t>90206; 138529</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>28670</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23979</t>
+          <t>28130</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>56800</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17647; 36703</t>
+          <t>19748; 41036</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17545; 33322</t>
+          <t>20084; 38269</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37762; 63305</t>
+          <t>43800; 70775</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>27174</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>25730</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52904</t>
+          <t>65657</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17293; 43341</t>
+          <t>20884; 49647</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14544; 41517</t>
+          <t>23834; 48595</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36060; 73572</t>
+          <t>49486; 88564</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>10638</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11403</t>
+          <t>15877</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>654; 5332</t>
+          <t>1988; 10952</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4436; 17074</t>
+          <t>6289; 17582</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6605; 19208</t>
+          <t>10185; 24310</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>30060</t>
+          <t>33469</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21175</t>
+          <t>22717</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51236</t>
+          <t>56187</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>22939; 41760</t>
+          <t>24279; 44550</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15010; 27889</t>
+          <t>16548; 30360</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40877; 62102</t>
+          <t>44379; 69451</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>29995</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>272588</t>
+          <t>84974</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>302583</t>
+          <t>125019</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>20087; 42032</t>
+          <t>28562; 55295</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83990; 566191</t>
+          <t>69446; 104101</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>106171; 738241</t>
+          <t>104495; 145934</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>121197</t>
+          <t>140327</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>133030</t>
+          <t>147553</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>254227</t>
+          <t>287880</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>45276; 172027</t>
+          <t>120509; 162812</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>114973; 153232</t>
+          <t>128429; 168357</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>162756; 308949</t>
+          <t>261278; 317449</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>306958</t>
+          <t>353173</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>541409</t>
+          <t>386194</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>848367</t>
+          <t>739367</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>236586; 347832</t>
+          <t>318421; 394750</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>342711; 1145201</t>
+          <t>353518; 423867</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>636630; 1465444</t>
+          <t>687566; 798216</t>
         </is>
       </c>
     </row>
